--- a/data/input.xlsx
+++ b/data/input.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temp\AllCode\Cursor\hy.cursor.consolidate\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temp\AllCode\hy.cursor.consolidate\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BE6E4B-A27E-43D1-886F-ABD0989C5377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF6B2E2-A999-4963-B0AB-8595464F429A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="417">
   <si>
     <t>Name</t>
   </si>
@@ -1404,6 +1404,12 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Wenning Fu</t>
+  </si>
+  <si>
+    <t>wenning.fu@broadcom.com</t>
   </si>
 </sst>
 </file>
@@ -8612,13 +8618,9 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.28515625" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
-    <col min="10" max="10" width="21.28515625" customWidth="1"/>
-    <col min="11" max="12" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="6" max="12" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8669,14 +8671,17 @@
       <c r="B2" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C2" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D2" s="36" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="E2" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F2" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G2" s="38">
         <v>0</v>
@@ -8685,16 +8690,16 @@
         <v>0</v>
       </c>
       <c r="I2" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="40">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K2" s="40">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="L2" s="40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="40">
         <v>0</v>
@@ -8707,14 +8712,17 @@
       <c r="B3" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C3" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D3" s="36" t="s">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="E3" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F3" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="38">
         <v>0</v>
@@ -8723,16 +8731,16 @@
         <v>0</v>
       </c>
       <c r="I3" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="40">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K3" s="40">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L3" s="40">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M3" s="40">
         <v>0</v>
@@ -8745,14 +8753,17 @@
       <c r="B4" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C4" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D4" s="36" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="E4" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F4" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="38">
         <v>0</v>
@@ -8761,13 +8772,13 @@
         <v>0</v>
       </c>
       <c r="I4" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="40">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K4" s="40">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L4" s="40">
         <v>0</v>
@@ -8783,14 +8794,17 @@
       <c r="B5" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C5" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D5" s="36" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="E5" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F5" s="38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G5" s="38">
         <v>0</v>
@@ -8799,16 +8813,16 @@
         <v>0</v>
       </c>
       <c r="I5" s="38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J5" s="40">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="K5" s="40">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="L5" s="40">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M5" s="40">
         <v>0</v>
@@ -8821,14 +8835,17 @@
       <c r="B6" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C6" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D6" s="36" t="s">
-        <v>16</v>
+        <v>183</v>
       </c>
       <c r="E6" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F6" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G6" s="38">
         <v>0</v>
@@ -8837,13 +8854,13 @@
         <v>0</v>
       </c>
       <c r="I6" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="40">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="K6" s="40">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="L6" s="40">
         <v>0</v>
@@ -8859,14 +8876,17 @@
       <c r="B7" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C7" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D7" s="36" t="s">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="E7" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F7" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="38">
         <v>0</v>
@@ -8875,16 +8895,16 @@
         <v>0</v>
       </c>
       <c r="I7" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" s="40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="40">
         <v>0</v>
@@ -8897,29 +8917,32 @@
       <c r="B8" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C8" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D8" s="36" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="E8" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F8" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G8" s="38">
-        <v>17.45</v>
+        <v>0</v>
       </c>
       <c r="H8" s="39">
-        <v>1.7450000000000001</v>
+        <v>0</v>
       </c>
       <c r="I8" s="38">
-        <v>-7.4499999999999993</v>
+        <v>0</v>
       </c>
       <c r="J8" s="40">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="K8" s="40">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="L8" s="40">
         <v>0</v>
@@ -8935,11 +8958,14 @@
       <c r="B9" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C9" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D9" s="36" t="s">
-        <v>181</v>
+        <v>116</v>
       </c>
       <c r="E9" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F9" s="38">
         <v>0</v>
@@ -8973,14 +8999,17 @@
       <c r="B10" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C10" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D10" s="36" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="E10" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F10" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="38">
         <v>0</v>
@@ -8989,13 +9018,13 @@
         <v>0</v>
       </c>
       <c r="I10" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L10" s="40">
         <v>0</v>
@@ -9011,14 +9040,17 @@
       <c r="B11" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C11" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D11" s="36" t="s">
-        <v>206</v>
+        <v>117</v>
       </c>
       <c r="E11" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F11" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="38">
         <v>0</v>
@@ -9027,13 +9059,13 @@
         <v>0</v>
       </c>
       <c r="I11" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="40">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K11" s="40">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L11" s="40">
         <v>0</v>
@@ -9049,14 +9081,17 @@
       <c r="B12" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C12" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D12" s="36" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="E12" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F12" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="38">
         <v>0</v>
@@ -9065,13 +9100,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="40">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K12" s="40">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L12" s="40">
         <v>0</v>
@@ -9087,14 +9122,17 @@
       <c r="B13" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C13" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D13" s="36" t="s">
-        <v>134</v>
+        <v>210</v>
       </c>
       <c r="E13" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F13" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G13" s="38">
         <v>0</v>
@@ -9103,13 +9141,13 @@
         <v>0</v>
       </c>
       <c r="I13" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J13" s="40">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K13" s="40">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L13" s="40">
         <v>0</v>
@@ -9125,14 +9163,17 @@
       <c r="B14" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C14" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D14" s="36" t="s">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="E14" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F14" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="38">
         <v>0</v>
@@ -9141,13 +9182,13 @@
         <v>0</v>
       </c>
       <c r="I14" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="40">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K14" s="40">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L14" s="40">
         <v>0</v>
@@ -9163,14 +9204,17 @@
       <c r="B15" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C15" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D15" s="36" t="s">
-        <v>28</v>
+        <v>202</v>
       </c>
       <c r="E15" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F15" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G15" s="38">
         <v>0</v>
@@ -9179,19 +9223,19 @@
         <v>0</v>
       </c>
       <c r="I15" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15" s="40">
-        <v>363</v>
+        <v>0</v>
       </c>
       <c r="K15" s="40">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="L15" s="40">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M15" s="40">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9201,14 +9245,17 @@
       <c r="B16" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C16" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D16" s="36" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="E16" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F16" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="38">
         <v>0</v>
@@ -9217,13 +9264,13 @@
         <v>0</v>
       </c>
       <c r="I16" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="40">
         <v>0</v>
@@ -9239,14 +9286,17 @@
       <c r="B17" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C17" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D17" s="36" t="s">
-        <v>31</v>
+        <v>204</v>
       </c>
       <c r="E17" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F17" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G17" s="38">
         <v>0</v>
@@ -9255,16 +9305,16 @@
         <v>0</v>
       </c>
       <c r="I17" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J17" s="40">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="K17" s="40">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="L17" s="40">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M17" s="40">
         <v>0</v>
@@ -9277,14 +9327,17 @@
       <c r="B18" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C18" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D18" s="36" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E18" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F18" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="38">
         <v>0</v>
@@ -9293,19 +9346,19 @@
         <v>0</v>
       </c>
       <c r="I18" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="40">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="K18" s="40">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L18" s="40">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M18" s="40">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9315,14 +9368,17 @@
       <c r="B19" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C19" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D19" s="36" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="E19" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F19" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="38">
         <v>0</v>
@@ -9331,13 +9387,13 @@
         <v>0</v>
       </c>
       <c r="I19" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="40">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K19" s="40">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L19" s="40">
         <v>0</v>
@@ -9353,14 +9409,17 @@
       <c r="B20" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C20" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D20" s="36" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="E20" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F20" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="38">
         <v>0</v>
@@ -9369,13 +9428,13 @@
         <v>0</v>
       </c>
       <c r="I20" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="40">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="K20" s="40">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="L20" s="40">
         <v>0</v>
@@ -9391,29 +9450,32 @@
       <c r="B21" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C21" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D21" s="36" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="E21" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F21" s="38">
+        <v>0</v>
+      </c>
+      <c r="G21" s="38">
+        <v>0</v>
+      </c>
+      <c r="H21" s="39">
+        <v>0</v>
+      </c>
+      <c r="I21" s="38">
+        <v>0</v>
+      </c>
+      <c r="J21" s="40">
         <v>1</v>
       </c>
-      <c r="G21" s="38">
-        <v>0</v>
-      </c>
-      <c r="H21" s="39">
-        <v>0</v>
-      </c>
-      <c r="I21" s="38">
+      <c r="K21" s="40">
         <v>1</v>
-      </c>
-      <c r="J21" s="40">
-        <v>0</v>
-      </c>
-      <c r="K21" s="40">
-        <v>0</v>
       </c>
       <c r="L21" s="40">
         <v>0</v>
@@ -9429,11 +9491,14 @@
       <c r="B22" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C22" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D22" s="36" t="s">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="E22" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F22" s="38">
         <v>0</v>
@@ -9448,13 +9513,13 @@
         <v>0</v>
       </c>
       <c r="J22" s="40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="40">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M22" s="40">
         <v>0</v>
@@ -9467,14 +9532,17 @@
       <c r="B23" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C23" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D23" s="36" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="E23" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F23" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G23" s="38">
         <v>0</v>
@@ -9483,13 +9551,13 @@
         <v>0</v>
       </c>
       <c r="I23" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J23" s="40">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="K23" s="40">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="L23" s="40">
         <v>0</v>
@@ -9505,14 +9573,17 @@
       <c r="B24" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C24" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D24" s="36" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="E24" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F24" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G24" s="38">
         <v>0</v>
@@ -9521,16 +9592,16 @@
         <v>0</v>
       </c>
       <c r="I24" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J24" s="40">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="K24" s="40">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="L24" s="40">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M24" s="40">
         <v>0</v>
@@ -9543,14 +9614,17 @@
       <c r="B25" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C25" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D25" s="36" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="E25" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F25" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="38">
         <v>0</v>
@@ -9559,16 +9633,16 @@
         <v>0</v>
       </c>
       <c r="I25" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" s="40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="40">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="M25" s="40">
         <v>0</v>
@@ -9581,14 +9655,17 @@
       <c r="B26" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C26" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D26" s="36" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="E26" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F26" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="38">
         <v>0</v>
@@ -9597,16 +9674,16 @@
         <v>0</v>
       </c>
       <c r="I26" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" s="40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" s="40">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M26" s="40">
         <v>0</v>
@@ -9619,14 +9696,17 @@
       <c r="B27" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C27" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D27" s="36" t="s">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="E27" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F27" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="38">
         <v>0</v>
@@ -9635,19 +9715,19 @@
         <v>0</v>
       </c>
       <c r="I27" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="40">
-        <v>233</v>
+        <v>2</v>
       </c>
       <c r="K27" s="40">
-        <v>233</v>
+        <v>2</v>
       </c>
       <c r="L27" s="40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="40">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9657,35 +9737,38 @@
       <c r="B28" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C28" s="36" t="s">
+        <v>177</v>
+      </c>
       <c r="D28" s="36" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="E28" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F28" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G28" s="38">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="H28" s="39">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="I28" s="38">
-        <v>-0.30000000000000071</v>
+        <v>0</v>
       </c>
       <c r="J28" s="40">
-        <v>488</v>
+        <v>3</v>
       </c>
       <c r="K28" s="40">
-        <v>805.8</v>
+        <v>3</v>
       </c>
       <c r="L28" s="40">
-        <v>855</v>
+        <v>29</v>
       </c>
       <c r="M28" s="40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9695,35 +9778,38 @@
       <c r="B29" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C29" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D29" s="36" t="s">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="E29" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F29" s="38">
+        <v>0</v>
+      </c>
+      <c r="G29" s="38">
+        <v>0</v>
+      </c>
+      <c r="H29" s="39">
+        <v>0</v>
+      </c>
+      <c r="I29" s="38">
+        <v>0</v>
+      </c>
+      <c r="J29" s="40">
+        <v>3</v>
+      </c>
+      <c r="K29" s="40">
+        <v>3</v>
+      </c>
+      <c r="L29" s="40">
+        <v>5</v>
+      </c>
+      <c r="M29" s="40">
         <v>1</v>
-      </c>
-      <c r="G29" s="38">
-        <v>0</v>
-      </c>
-      <c r="H29" s="39">
-        <v>0</v>
-      </c>
-      <c r="I29" s="38">
-        <v>1</v>
-      </c>
-      <c r="J29" s="40">
-        <v>129</v>
-      </c>
-      <c r="K29" s="40">
-        <v>125</v>
-      </c>
-      <c r="L29" s="40">
-        <v>465</v>
-      </c>
-      <c r="M29" s="40">
-        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9733,14 +9819,17 @@
       <c r="B30" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C30" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D30" s="36" t="s">
-        <v>39</v>
+        <v>151</v>
       </c>
       <c r="E30" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F30" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G30" s="38">
         <v>0</v>
@@ -9749,13 +9838,13 @@
         <v>0</v>
       </c>
       <c r="I30" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J30" s="40">
-        <v>107</v>
+        <v>3</v>
       </c>
       <c r="K30" s="40">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="L30" s="40">
         <v>0</v>
@@ -9771,14 +9860,17 @@
       <c r="B31" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C31" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D31" s="36" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E31" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F31" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="38">
         <v>0</v>
@@ -9787,13 +9879,13 @@
         <v>0</v>
       </c>
       <c r="I31" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K31" s="40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L31" s="40">
         <v>0</v>
@@ -9809,14 +9901,17 @@
       <c r="B32" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C32" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D32" s="36" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="E32" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F32" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G32" s="38">
         <v>0</v>
@@ -9825,16 +9920,16 @@
         <v>0</v>
       </c>
       <c r="I32" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J32" s="40">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="K32" s="40">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="L32" s="40">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M32" s="40">
         <v>0</v>
@@ -9847,11 +9942,14 @@
       <c r="B33" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C33" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D33" s="36" t="s">
-        <v>197</v>
+        <v>67</v>
       </c>
       <c r="E33" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F33" s="38">
         <v>0</v>
@@ -9866,10 +9964,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="40">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K33" s="40">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L33" s="40">
         <v>0</v>
@@ -9885,14 +9983,17 @@
       <c r="B34" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C34" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D34" s="36" t="s">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="E34" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F34" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="38">
         <v>0</v>
@@ -9901,19 +10002,19 @@
         <v>0</v>
       </c>
       <c r="I34" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="40">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="K34" s="40">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="L34" s="40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9923,11 +10024,14 @@
       <c r="B35" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C35" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D35" s="36" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="E35" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F35" s="38">
         <v>0</v>
@@ -9942,10 +10046,10 @@
         <v>0</v>
       </c>
       <c r="J35" s="40">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K35" s="40">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L35" s="40">
         <v>0</v>
@@ -9961,14 +10065,17 @@
       <c r="B36" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C36" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D36" s="36" t="s">
-        <v>186</v>
+        <v>18</v>
       </c>
       <c r="E36" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F36" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G36" s="38">
         <v>0</v>
@@ -9977,16 +10084,16 @@
         <v>0</v>
       </c>
       <c r="I36" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J36" s="40">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="K36" s="40">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="L36" s="40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="40">
         <v>0</v>
@@ -9999,11 +10106,14 @@
       <c r="B37" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C37" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D37" s="36" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F37" s="38">
         <v>0</v>
@@ -10018,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="J37" s="40">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K37" s="40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L37" s="40">
         <v>0</v>
@@ -10037,14 +10147,17 @@
       <c r="B38" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C38" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D38" s="36" t="s">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="E38" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F38" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="38">
         <v>0</v>
@@ -10053,13 +10166,13 @@
         <v>0</v>
       </c>
       <c r="I38" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="40">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K38" s="40">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L38" s="40">
         <v>0</v>
@@ -10075,14 +10188,17 @@
       <c r="B39" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C39" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D39" s="36" t="s">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="E39" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F39" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="38">
         <v>0</v>
@@ -10091,16 +10207,16 @@
         <v>0</v>
       </c>
       <c r="I39" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="40">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="K39" s="40">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="L39" s="40">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M39" s="40">
         <v>0</v>
@@ -10113,14 +10229,17 @@
       <c r="B40" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C40" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D40" s="36" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E40" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F40" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G40" s="38">
         <v>0</v>
@@ -10129,19 +10248,19 @@
         <v>0</v>
       </c>
       <c r="I40" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J40" s="40">
-        <v>248</v>
+        <v>9</v>
       </c>
       <c r="K40" s="40">
-        <v>253</v>
+        <v>9</v>
       </c>
       <c r="L40" s="40">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="M40" s="40">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10151,14 +10270,17 @@
       <c r="B41" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C41" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D41" s="36" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="E41" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F41" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="38">
         <v>0</v>
@@ -10167,19 +10289,19 @@
         <v>0</v>
       </c>
       <c r="I41" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="40">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K41" s="40">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L41" s="40">
-        <v>5</v>
+        <v>210</v>
       </c>
       <c r="M41" s="40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10189,14 +10311,17 @@
       <c r="B42" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C42" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D42" s="36" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="E42" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F42" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="38">
         <v>0</v>
@@ -10205,13 +10330,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="40">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="K42" s="40">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="L42" s="40">
         <v>0</v>
@@ -10227,14 +10352,17 @@
       <c r="B43" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C43" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D43" s="36" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="E43" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F43" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="38">
         <v>0</v>
@@ -10243,16 +10371,16 @@
         <v>0</v>
       </c>
       <c r="I43" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="40">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="K43" s="40">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="L43" s="40">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M43" s="40">
         <v>0</v>
@@ -10265,14 +10393,17 @@
       <c r="B44" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C44" s="36" t="s">
+        <v>177</v>
+      </c>
       <c r="D44" s="36" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="E44" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F44" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="38">
         <v>0</v>
@@ -10281,19 +10412,19 @@
         <v>0</v>
       </c>
       <c r="I44" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="40">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="K44" s="40">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L44" s="40">
         <v>0</v>
       </c>
       <c r="M44" s="40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10303,32 +10434,35 @@
       <c r="B45" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C45" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D45" s="36" t="s">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="E45" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F45" s="38">
+        <v>0</v>
+      </c>
+      <c r="G45" s="38">
+        <v>0</v>
+      </c>
+      <c r="H45" s="39">
+        <v>0</v>
+      </c>
+      <c r="I45" s="38">
+        <v>0</v>
+      </c>
+      <c r="J45" s="40">
+        <v>13</v>
+      </c>
+      <c r="K45" s="40">
+        <v>13</v>
+      </c>
+      <c r="L45" s="40">
         <v>1</v>
-      </c>
-      <c r="G45" s="38">
-        <v>0</v>
-      </c>
-      <c r="H45" s="39">
-        <v>0</v>
-      </c>
-      <c r="I45" s="38">
-        <v>1</v>
-      </c>
-      <c r="J45" s="40">
-        <v>0</v>
-      </c>
-      <c r="K45" s="40">
-        <v>0</v>
-      </c>
-      <c r="L45" s="40">
-        <v>0</v>
       </c>
       <c r="M45" s="40">
         <v>0</v>
@@ -10341,11 +10475,14 @@
       <c r="B46" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C46" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D46" s="36" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="E46" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F46" s="38">
         <v>0</v>
@@ -10360,10 +10497,10 @@
         <v>0</v>
       </c>
       <c r="J46" s="40">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K46" s="40">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L46" s="40">
         <v>0</v>
@@ -10379,14 +10516,17 @@
       <c r="B47" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C47" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D47" s="36" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="E47" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F47" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="38">
         <v>0</v>
@@ -10395,19 +10535,19 @@
         <v>0</v>
       </c>
       <c r="I47" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="40">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="K47" s="40">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="L47" s="40">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="M47" s="40">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10417,11 +10557,14 @@
       <c r="B48" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C48" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D48" s="36" t="s">
-        <v>55</v>
+        <v>206</v>
       </c>
       <c r="E48" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F48" s="38">
         <v>0</v>
@@ -10436,13 +10579,13 @@
         <v>0</v>
       </c>
       <c r="J48" s="40">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K48" s="40">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L48" s="40">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M48" s="40">
         <v>0</v>
@@ -10455,14 +10598,17 @@
       <c r="B49" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C49" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D49" s="36" t="s">
-        <v>57</v>
+        <v>185</v>
       </c>
       <c r="E49" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F49" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" s="38">
         <v>0</v>
@@ -10471,13 +10617,13 @@
         <v>0</v>
       </c>
       <c r="I49" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="40">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K49" s="40">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="L49" s="40">
         <v>0</v>
@@ -10493,32 +10639,35 @@
       <c r="B50" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C50" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D50" s="36" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E50" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F50" s="38">
+        <v>0</v>
+      </c>
+      <c r="G50" s="38">
+        <v>0</v>
+      </c>
+      <c r="H50" s="39">
+        <v>0</v>
+      </c>
+      <c r="I50" s="38">
+        <v>0</v>
+      </c>
+      <c r="J50" s="40">
+        <v>23</v>
+      </c>
+      <c r="K50" s="40">
+        <v>22</v>
+      </c>
+      <c r="L50" s="40">
         <v>1</v>
-      </c>
-      <c r="G50" s="38">
-        <v>0</v>
-      </c>
-      <c r="H50" s="39">
-        <v>0</v>
-      </c>
-      <c r="I50" s="38">
-        <v>1</v>
-      </c>
-      <c r="J50" s="40">
-        <v>119</v>
-      </c>
-      <c r="K50" s="40">
-        <v>121</v>
-      </c>
-      <c r="L50" s="40">
-        <v>310</v>
       </c>
       <c r="M50" s="40">
         <v>0</v>
@@ -10531,14 +10680,17 @@
       <c r="B51" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C51" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D51" s="36" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="E51" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F51" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="38">
         <v>0</v>
@@ -10547,16 +10699,16 @@
         <v>0</v>
       </c>
       <c r="I51" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" s="40">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="K51" s="40">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L51" s="40">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M51" s="40">
         <v>0</v>
@@ -10569,14 +10721,17 @@
       <c r="B52" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C52" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D52" s="36" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="E52" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F52" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="38">
         <v>0</v>
@@ -10585,13 +10740,13 @@
         <v>0</v>
       </c>
       <c r="I52" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" s="40">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K52" s="40">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="L52" s="40">
         <v>0</v>
@@ -10607,14 +10762,17 @@
       <c r="B53" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C53" s="36" t="s">
+        <v>177</v>
+      </c>
       <c r="D53" s="36" t="s">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="E53" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F53" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="38">
         <v>0</v>
@@ -10623,13 +10781,13 @@
         <v>0</v>
       </c>
       <c r="I53" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="40">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K53" s="40">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="L53" s="40">
         <v>0</v>
@@ -10645,14 +10803,17 @@
       <c r="B54" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C54" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D54" s="36" t="s">
-        <v>63</v>
+        <v>149</v>
       </c>
       <c r="E54" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F54" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="38">
         <v>0</v>
@@ -10661,13 +10822,13 @@
         <v>0</v>
       </c>
       <c r="I54" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="40">
-        <v>453</v>
+        <v>24</v>
       </c>
       <c r="K54" s="40">
-        <v>416</v>
+        <v>24</v>
       </c>
       <c r="L54" s="40">
         <v>0</v>
@@ -10683,14 +10844,17 @@
       <c r="B55" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C55" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D55" s="36" t="s">
         <v>65</v>
       </c>
       <c r="E55" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F55" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="38">
         <v>0</v>
@@ -10699,7 +10863,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="40">
         <v>25</v>
@@ -10721,14 +10885,17 @@
       <c r="B56" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C56" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D56" s="36" t="s">
-        <v>67</v>
+        <v>184</v>
       </c>
       <c r="E56" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F56" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="38">
         <v>0</v>
@@ -10737,16 +10904,16 @@
         <v>0</v>
       </c>
       <c r="I56" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="40">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K56" s="40">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="L56" s="40">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M56" s="40">
         <v>0</v>
@@ -10759,14 +10926,17 @@
       <c r="B57" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C57" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D57" s="36" t="s">
-        <v>195</v>
+        <v>52</v>
       </c>
       <c r="E57" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F57" s="38">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G57" s="38">
         <v>0</v>
@@ -10775,19 +10945,19 @@
         <v>0</v>
       </c>
       <c r="I57" s="38">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J57" s="40">
-        <v>162</v>
+        <v>32</v>
       </c>
       <c r="K57" s="40">
-        <v>183</v>
+        <v>25</v>
       </c>
       <c r="L57" s="40">
-        <v>290</v>
+        <v>1</v>
       </c>
       <c r="M57" s="40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10797,14 +10967,17 @@
       <c r="B58" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C58" s="36" t="s">
+        <v>177</v>
+      </c>
       <c r="D58" s="36" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E58" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F58" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="38">
         <v>0</v>
@@ -10813,19 +10986,19 @@
         <v>0</v>
       </c>
       <c r="I58" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" s="40">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="K58" s="40">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="L58" s="40">
-        <v>81</v>
+        <v>233</v>
       </c>
       <c r="M58" s="40">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10835,14 +11008,17 @@
       <c r="B59" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C59" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D59" s="36" t="s">
-        <v>210</v>
+        <v>88</v>
       </c>
       <c r="E59" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F59" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G59" s="38">
         <v>0</v>
@@ -10851,13 +11027,13 @@
         <v>0</v>
       </c>
       <c r="I59" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J59" s="40">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K59" s="40">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L59" s="40">
         <v>0</v>
@@ -10873,11 +11049,14 @@
       <c r="B60" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C60" s="36" t="s">
+        <v>177</v>
+      </c>
       <c r="D60" s="36" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="E60" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F60" s="38">
         <v>0</v>
@@ -10892,10 +11071,10 @@
         <v>0</v>
       </c>
       <c r="J60" s="40">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K60" s="40">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L60" s="40">
         <v>0</v>
@@ -10911,14 +11090,17 @@
       <c r="B61" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C61" s="36" t="s">
+        <v>177</v>
+      </c>
       <c r="D61" s="36" t="s">
-        <v>202</v>
+        <v>126</v>
       </c>
       <c r="E61" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F61" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="38">
         <v>0</v>
@@ -10927,16 +11109,16 @@
         <v>0</v>
       </c>
       <c r="I61" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="40">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K61" s="40">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L61" s="40">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M61" s="40">
         <v>0</v>
@@ -10949,14 +11131,17 @@
       <c r="B62" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C62" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D62" s="36" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E62" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F62" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" s="38">
         <v>0</v>
@@ -10965,16 +11150,16 @@
         <v>0</v>
       </c>
       <c r="I62" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="40">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="K62" s="40">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="L62" s="40">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M62" s="40">
         <v>0</v>
@@ -10987,14 +11172,17 @@
       <c r="B63" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C63" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D63" s="36" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="E63" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F63" s="38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G63" s="38">
         <v>0</v>
@@ -11003,19 +11191,19 @@
         <v>0</v>
       </c>
       <c r="I63" s="38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J63" s="40">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="K63" s="40">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="L63" s="40">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="M63" s="40">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11025,14 +11213,17 @@
       <c r="B64" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C64" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D64" s="36" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="E64" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F64" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" s="38">
         <v>0</v>
@@ -11041,16 +11232,16 @@
         <v>0</v>
       </c>
       <c r="I64" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" s="40">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="K64" s="40">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="L64" s="40">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="M64" s="40">
         <v>0</v>
@@ -11063,14 +11254,17 @@
       <c r="B65" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C65" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D65" s="36" t="s">
-        <v>142</v>
+        <v>207</v>
       </c>
       <c r="E65" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F65" s="38">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G65" s="38">
         <v>0</v>
@@ -11079,13 +11273,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="38">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J65" s="40">
-        <v>500</v>
+        <v>51</v>
       </c>
       <c r="K65" s="40">
-        <v>691</v>
+        <v>51</v>
       </c>
       <c r="L65" s="40">
         <v>0</v>
@@ -11101,14 +11295,17 @@
       <c r="B66" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C66" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D66" s="36" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="E66" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F66" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="38">
         <v>0</v>
@@ -11117,16 +11314,16 @@
         <v>0</v>
       </c>
       <c r="I66" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" s="40">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K66" s="40">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="L66" s="40">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="M66" s="40">
         <v>0</v>
@@ -11139,14 +11336,17 @@
       <c r="B67" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C67" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D67" s="36" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="E67" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F67" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" s="38">
         <v>0</v>
@@ -11155,16 +11355,16 @@
         <v>0</v>
       </c>
       <c r="I67" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="40">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="K67" s="40">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="L67" s="40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M67" s="40">
         <v>0</v>
@@ -11177,14 +11377,17 @@
       <c r="B68" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C68" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D68" s="36" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="E68" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F68" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="38">
         <v>0</v>
@@ -11193,16 +11396,16 @@
         <v>0</v>
       </c>
       <c r="I68" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" s="40">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="K68" s="40">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="L68" s="40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M68" s="40">
         <v>0</v>
@@ -11215,14 +11418,17 @@
       <c r="B69" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C69" s="36" t="s">
+        <v>177</v>
+      </c>
       <c r="D69" s="36" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="E69" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F69" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="38">
         <v>0</v>
@@ -11231,16 +11437,16 @@
         <v>0</v>
       </c>
       <c r="I69" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="40">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K69" s="40">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L69" s="40">
-        <v>64</v>
+        <v>288</v>
       </c>
       <c r="M69" s="40">
         <v>0</v>
@@ -11253,11 +11459,14 @@
       <c r="B70" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C70" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D70" s="36" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E70" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F70" s="38">
         <v>0</v>
@@ -11272,16 +11481,16 @@
         <v>0</v>
       </c>
       <c r="J70" s="40">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="K70" s="40">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L70" s="40">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M70" s="40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11291,14 +11500,17 @@
       <c r="B71" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C71" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D71" s="36" t="s">
-        <v>209</v>
+        <v>134</v>
       </c>
       <c r="E71" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F71" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G71" s="38">
         <v>0</v>
@@ -11307,16 +11519,16 @@
         <v>0</v>
       </c>
       <c r="I71" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J71" s="40">
-        <v>206</v>
+        <v>66</v>
       </c>
       <c r="K71" s="40">
-        <v>206</v>
+        <v>62</v>
       </c>
       <c r="L71" s="40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M71" s="40">
         <v>0</v>
@@ -11329,11 +11541,14 @@
       <c r="B72" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C72" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D72" s="36" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E72" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F72" s="38">
         <v>0</v>
@@ -11348,13 +11563,13 @@
         <v>0</v>
       </c>
       <c r="J72" s="40">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="K72" s="40">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L72" s="40">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M72" s="40">
         <v>0</v>
@@ -11367,14 +11582,17 @@
       <c r="B73" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C73" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D73" s="36" t="s">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="E73" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F73" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" s="38">
         <v>0</v>
@@ -11383,16 +11601,16 @@
         <v>0</v>
       </c>
       <c r="I73" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="40">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="K73" s="40">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="L73" s="40">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="M73" s="40">
         <v>0</v>
@@ -11405,14 +11623,17 @@
       <c r="B74" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C74" s="36" t="s">
+        <v>177</v>
+      </c>
       <c r="D74" s="36" t="s">
-        <v>203</v>
+        <v>123</v>
       </c>
       <c r="E74" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F74" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="38">
         <v>0</v>
@@ -11421,19 +11642,19 @@
         <v>0</v>
       </c>
       <c r="I74" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" s="40">
-        <v>177</v>
+        <v>65</v>
       </c>
       <c r="K74" s="40">
-        <v>177</v>
+        <v>65</v>
       </c>
       <c r="L74" s="40">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M74" s="40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11443,14 +11664,17 @@
       <c r="B75" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C75" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D75" s="36" t="s">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="E75" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F75" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="38">
         <v>0</v>
@@ -11459,16 +11683,16 @@
         <v>0</v>
       </c>
       <c r="I75" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" s="40">
-        <v>191</v>
+        <v>69</v>
       </c>
       <c r="K75" s="40">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="L75" s="40">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M75" s="40">
         <v>0</v>
@@ -11481,14 +11705,17 @@
       <c r="B76" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C76" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D76" s="36" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="E76" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F76" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="38">
         <v>0</v>
@@ -11497,13 +11724,13 @@
         <v>0</v>
       </c>
       <c r="I76" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" s="40">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="K76" s="40">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="L76" s="40">
         <v>0</v>
@@ -11519,14 +11746,17 @@
       <c r="B77" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C77" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D77" s="36" t="s">
-        <v>207</v>
+        <v>70</v>
       </c>
       <c r="E77" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F77" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="38">
         <v>0</v>
@@ -11535,16 +11765,16 @@
         <v>0</v>
       </c>
       <c r="I77" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" s="40">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="K77" s="40">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="L77" s="40">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M77" s="40">
         <v>0</v>
@@ -11557,14 +11787,17 @@
       <c r="B78" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C78" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D78" s="36" t="s">
-        <v>208</v>
+        <v>43</v>
       </c>
       <c r="E78" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F78" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G78" s="38">
         <v>0</v>
@@ -11573,16 +11806,16 @@
         <v>0</v>
       </c>
       <c r="I78" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J78" s="40">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="K78" s="40">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="L78" s="40">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M78" s="40">
         <v>0</v>
@@ -11595,14 +11828,17 @@
       <c r="B79" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C79" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D79" s="36" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E79" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F79" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="38">
         <v>0</v>
@@ -11611,16 +11847,16 @@
         <v>0</v>
       </c>
       <c r="I79" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" s="40">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="K79" s="40">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="L79" s="40">
-        <v>1</v>
+        <v>319</v>
       </c>
       <c r="M79" s="40">
         <v>0</v>
@@ -11633,14 +11869,17 @@
       <c r="B80" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C80" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D80" s="36" t="s">
-        <v>184</v>
+        <v>119</v>
       </c>
       <c r="E80" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F80" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" s="38">
         <v>0</v>
@@ -11649,16 +11888,16 @@
         <v>0</v>
       </c>
       <c r="I80" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="40">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="K80" s="40">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="L80" s="40">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M80" s="40">
         <v>0</v>
@@ -11671,14 +11910,17 @@
       <c r="B81" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C81" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D81" s="36" t="s">
-        <v>147</v>
+        <v>61</v>
       </c>
       <c r="E81" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F81" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" s="38">
         <v>0</v>
@@ -11687,16 +11929,16 @@
         <v>0</v>
       </c>
       <c r="I81" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="40">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="K81" s="40">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="L81" s="40">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M81" s="40">
         <v>0</v>
@@ -11709,14 +11951,17 @@
       <c r="B82" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C82" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D82" s="36" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="E82" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F82" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" s="38">
         <v>0</v>
@@ -11725,19 +11970,19 @@
         <v>0</v>
       </c>
       <c r="I82" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="40">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="K82" s="40">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="L82" s="40">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M82" s="40">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11747,14 +11992,17 @@
       <c r="B83" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C83" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D83" s="36" t="s">
-        <v>144</v>
+        <v>37</v>
       </c>
       <c r="E83" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F83" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="38">
         <v>0</v>
@@ -11763,16 +12011,16 @@
         <v>0</v>
       </c>
       <c r="I83" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="40">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="K83" s="40">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="L83" s="40">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M83" s="40">
         <v>0</v>
@@ -11785,14 +12033,17 @@
       <c r="B84" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C84" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D84" s="36" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="E84" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F84" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G84" s="38">
         <v>0</v>
@@ -11801,16 +12052,16 @@
         <v>0</v>
       </c>
       <c r="I84" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J84" s="40">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="K84" s="40">
-        <v>324</v>
+        <v>80</v>
       </c>
       <c r="L84" s="40">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M84" s="40">
         <v>0</v>
@@ -11823,11 +12074,14 @@
       <c r="B85" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C85" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D85" s="36" t="s">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E85" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F85" s="38">
         <v>0</v>
@@ -11842,10 +12096,10 @@
         <v>0</v>
       </c>
       <c r="J85" s="40">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="K85" s="40">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L85" s="40">
         <v>0</v>
@@ -11861,14 +12115,17 @@
       <c r="B86" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C86" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D86" s="36" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E86" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F86" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="38">
         <v>0</v>
@@ -11877,13 +12134,13 @@
         <v>0</v>
       </c>
       <c r="I86" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" s="40">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="K86" s="40">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="L86" s="40">
         <v>0</v>
@@ -11899,14 +12156,17 @@
       <c r="B87" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C87" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D87" s="36" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="E87" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F87" s="38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G87" s="38">
         <v>0</v>
@@ -11915,19 +12175,19 @@
         <v>0</v>
       </c>
       <c r="I87" s="38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J87" s="40">
-        <v>441</v>
+        <v>103</v>
       </c>
       <c r="K87" s="40">
-        <v>447</v>
+        <v>95</v>
       </c>
       <c r="L87" s="40">
-        <v>474</v>
+        <v>6</v>
       </c>
       <c r="M87" s="40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11937,14 +12197,17 @@
       <c r="B88" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C88" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D88" s="36" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E88" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F88" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" s="38">
         <v>0</v>
@@ -11953,16 +12216,16 @@
         <v>0</v>
       </c>
       <c r="I88" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" s="40">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="K88" s="40">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="L88" s="40">
-        <v>9</v>
+        <v>827</v>
       </c>
       <c r="M88" s="40">
         <v>0</v>
@@ -11975,14 +12238,17 @@
       <c r="B89" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C89" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D89" s="36" t="s">
-        <v>194</v>
+        <v>96</v>
       </c>
       <c r="E89" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F89" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G89" s="38">
         <v>0</v>
@@ -11991,16 +12257,16 @@
         <v>0</v>
       </c>
       <c r="I89" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J89" s="40">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="K89" s="40">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="L89" s="40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M89" s="40">
         <v>0</v>
@@ -12013,35 +12279,38 @@
       <c r="B90" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C90" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D90" s="36" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="E90" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F90" s="38">
+        <v>0</v>
+      </c>
+      <c r="G90" s="38">
+        <v>0</v>
+      </c>
+      <c r="H90" s="39">
+        <v>0</v>
+      </c>
+      <c r="I90" s="38">
+        <v>0</v>
+      </c>
+      <c r="J90" s="40">
+        <v>124</v>
+      </c>
+      <c r="K90" s="40">
+        <v>115</v>
+      </c>
+      <c r="L90" s="40">
         <v>1</v>
       </c>
-      <c r="G90" s="38">
-        <v>0</v>
-      </c>
-      <c r="H90" s="39">
-        <v>0</v>
-      </c>
-      <c r="I90" s="38">
-        <v>1</v>
-      </c>
-      <c r="J90" s="40">
-        <v>30</v>
-      </c>
-      <c r="K90" s="40">
-        <v>26</v>
-      </c>
-      <c r="L90" s="40">
-        <v>17</v>
-      </c>
       <c r="M90" s="40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12051,11 +12320,14 @@
       <c r="B91" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C91" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D91" s="36" t="s">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="E91" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F91" s="38">
         <v>0</v>
@@ -12070,16 +12342,16 @@
         <v>0</v>
       </c>
       <c r="J91" s="40">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="K91" s="40">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="L91" s="40">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="M91" s="40">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12089,14 +12361,17 @@
       <c r="B92" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C92" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D92" s="36" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="E92" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F92" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G92" s="38">
         <v>0</v>
@@ -12105,13 +12380,13 @@
         <v>0</v>
       </c>
       <c r="I92" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J92" s="40">
-        <v>435</v>
+        <v>146</v>
       </c>
       <c r="K92" s="40">
-        <v>427</v>
+        <v>141</v>
       </c>
       <c r="L92" s="40">
         <v>0</v>
@@ -12127,11 +12402,14 @@
       <c r="B93" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C93" s="36" t="s">
+        <v>177</v>
+      </c>
       <c r="D93" s="36" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="E93" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F93" s="38">
         <v>0</v>
@@ -12146,16 +12424,16 @@
         <v>0</v>
       </c>
       <c r="J93" s="40">
-        <v>10</v>
+        <v>157</v>
       </c>
       <c r="K93" s="40">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="L93" s="40">
-        <v>114</v>
+        <v>595</v>
       </c>
       <c r="M93" s="40">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12165,14 +12443,17 @@
       <c r="B94" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C94" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D94" s="36" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E94" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F94" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G94" s="38">
         <v>0</v>
@@ -12181,16 +12462,16 @@
         <v>0</v>
       </c>
       <c r="I94" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J94" s="40">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="K94" s="40">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="L94" s="40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M94" s="40">
         <v>0</v>
@@ -12203,14 +12484,17 @@
       <c r="B95" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C95" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D95" s="36" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="E95" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F95" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="38">
         <v>0</v>
@@ -12219,13 +12503,13 @@
         <v>0</v>
       </c>
       <c r="I95" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" s="40">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="K95" s="40">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="L95" s="40">
         <v>0</v>
@@ -12241,14 +12525,17 @@
       <c r="B96" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C96" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D96" s="36" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="E96" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F96" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="38">
         <v>0</v>
@@ -12257,19 +12544,19 @@
         <v>0</v>
       </c>
       <c r="I96" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" s="40">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="K96" s="40">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="L96" s="40">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="M96" s="40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12279,14 +12566,17 @@
       <c r="B97" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C97" s="36" t="s">
+        <v>177</v>
+      </c>
       <c r="D97" s="36" t="s">
-        <v>204</v>
+        <v>125</v>
       </c>
       <c r="E97" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F97" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="38">
         <v>0</v>
@@ -12295,16 +12585,16 @@
         <v>0</v>
       </c>
       <c r="I97" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" s="40">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="K97" s="40">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="L97" s="40">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M97" s="40">
         <v>0</v>
@@ -12317,14 +12607,17 @@
       <c r="B98" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C98" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D98" s="36" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="E98" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F98" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="38">
         <v>0</v>
@@ -12333,16 +12626,16 @@
         <v>0</v>
       </c>
       <c r="I98" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" s="40">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="K98" s="40">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="L98" s="40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M98" s="40">
         <v>0</v>
@@ -12355,14 +12648,17 @@
       <c r="B99" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C99" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D99" s="36" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E99" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F99" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" s="38">
         <v>0</v>
@@ -12371,16 +12667,16 @@
         <v>0</v>
       </c>
       <c r="I99" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" s="40">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="K99" s="40">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="L99" s="40">
-        <v>293</v>
+        <v>2</v>
       </c>
       <c r="M99" s="40">
         <v>0</v>
@@ -12393,14 +12689,17 @@
       <c r="B100" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C100" s="36" t="s">
+        <v>182</v>
+      </c>
       <c r="D100" s="36" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E100" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F100" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G100" s="38">
         <v>0</v>
@@ -12409,13 +12708,13 @@
         <v>0</v>
       </c>
       <c r="I100" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J100" s="40">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="K100" s="40">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="L100" s="40">
         <v>0</v>
@@ -12431,35 +12730,38 @@
       <c r="B101" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C101" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D101" s="36" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="E101" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F101" s="38">
+        <v>20</v>
+      </c>
+      <c r="G101" s="38">
+        <v>0</v>
+      </c>
+      <c r="H101" s="39">
+        <v>0</v>
+      </c>
+      <c r="I101" s="38">
+        <v>20</v>
+      </c>
+      <c r="J101" s="40">
+        <v>184</v>
+      </c>
+      <c r="K101" s="40">
+        <v>184</v>
+      </c>
+      <c r="L101" s="40">
+        <v>296</v>
+      </c>
+      <c r="M101" s="40">
         <v>1</v>
-      </c>
-      <c r="G101" s="38">
-        <v>0</v>
-      </c>
-      <c r="H101" s="39">
-        <v>0</v>
-      </c>
-      <c r="I101" s="38">
-        <v>1</v>
-      </c>
-      <c r="J101" s="40">
-        <v>16</v>
-      </c>
-      <c r="K101" s="40">
-        <v>21</v>
-      </c>
-      <c r="L101" s="40">
-        <v>0</v>
-      </c>
-      <c r="M101" s="40">
-        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12469,14 +12771,17 @@
       <c r="B102" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C102" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D102" s="36" t="s">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="E102" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F102" s="38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G102" s="38">
         <v>0</v>
@@ -12485,16 +12790,16 @@
         <v>0</v>
       </c>
       <c r="I102" s="38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J102" s="40">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="K102" s="40">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="L102" s="40">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M102" s="40">
         <v>0</v>
@@ -12507,14 +12812,17 @@
       <c r="B103" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C103" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D103" s="36" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="E103" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F103" s="38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G103" s="38">
         <v>0</v>
@@ -12523,16 +12831,16 @@
         <v>0</v>
       </c>
       <c r="I103" s="38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J103" s="40">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="K103" s="40">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="L103" s="40">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M103" s="40">
         <v>0</v>
@@ -12545,14 +12853,17 @@
       <c r="B104" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C104" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D104" s="36" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
       <c r="E104" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F104" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" s="38">
         <v>0</v>
@@ -12561,16 +12872,16 @@
         <v>0</v>
       </c>
       <c r="I104" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="40">
-        <v>64</v>
+        <v>253</v>
       </c>
       <c r="K104" s="40">
-        <v>59</v>
+        <v>237</v>
       </c>
       <c r="L104" s="40">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M104" s="40">
         <v>0</v>
@@ -12583,14 +12894,17 @@
       <c r="B105" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C105" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D105" s="36" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="E105" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F105" s="38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G105" s="38">
         <v>0</v>
@@ -12599,19 +12913,19 @@
         <v>0</v>
       </c>
       <c r="I105" s="38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J105" s="40">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="K105" s="40">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="L105" s="40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M105" s="40">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12621,14 +12935,17 @@
       <c r="B106" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C106" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D106" s="36" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="E106" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F106" s="38">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G106" s="38">
         <v>0</v>
@@ -12637,16 +12954,16 @@
         <v>0</v>
       </c>
       <c r="I106" s="38">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J106" s="40">
-        <v>3</v>
+        <v>288</v>
       </c>
       <c r="K106" s="40">
-        <v>3</v>
+        <v>274</v>
       </c>
       <c r="L106" s="40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M106" s="40">
         <v>0</v>
@@ -12659,14 +12976,17 @@
       <c r="B107" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C107" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D107" s="36" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="E107" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F107" s="38">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G107" s="38">
         <v>0</v>
@@ -12675,16 +12995,16 @@
         <v>0</v>
       </c>
       <c r="I107" s="38">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J107" s="40">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="K107" s="40">
-        <v>77</v>
+        <v>284</v>
       </c>
       <c r="L107" s="40">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M107" s="40">
         <v>0</v>
@@ -12697,14 +13017,17 @@
       <c r="B108" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C108" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D108" s="36" t="s">
-        <v>100</v>
+        <v>209</v>
       </c>
       <c r="E108" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F108" s="38">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G108" s="38">
         <v>0</v>
@@ -12713,16 +13036,16 @@
         <v>0</v>
       </c>
       <c r="I108" s="38">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J108" s="40">
-        <v>9</v>
+        <v>294</v>
       </c>
       <c r="K108" s="40">
-        <v>9</v>
+        <v>286</v>
       </c>
       <c r="L108" s="40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M108" s="40">
         <v>0</v>
@@ -12735,14 +13058,17 @@
       <c r="B109" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C109" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D109" s="36" t="s">
-        <v>201</v>
+        <v>33</v>
       </c>
       <c r="E109" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F109" s="38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G109" s="38">
         <v>0</v>
@@ -12751,13 +13077,13 @@
         <v>0</v>
       </c>
       <c r="I109" s="38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J109" s="40">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="K109" s="40">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L109" s="40">
         <v>0</v>
@@ -12773,14 +13099,17 @@
       <c r="B110" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C110" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D110" s="36" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E110" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F110" s="38">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G110" s="38">
         <v>0</v>
@@ -12789,16 +13118,16 @@
         <v>0</v>
       </c>
       <c r="I110" s="38">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J110" s="40">
-        <v>14</v>
+        <v>367</v>
       </c>
       <c r="K110" s="40">
-        <v>23</v>
+        <v>363</v>
       </c>
       <c r="L110" s="40">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M110" s="40">
         <v>0</v>
@@ -12811,14 +13140,17 @@
       <c r="B111" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C111" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D111" s="36" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="E111" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F111" s="38">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G111" s="38">
         <v>0</v>
@@ -12827,16 +13159,16 @@
         <v>0</v>
       </c>
       <c r="I111" s="38">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J111" s="40">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="K111" s="40">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="L111" s="40">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M111" s="40">
         <v>0</v>
@@ -12849,14 +13181,17 @@
       <c r="B112" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C112" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D112" s="36" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="E112" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F112" s="38">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G112" s="38">
         <v>0</v>
@@ -12865,13 +13200,13 @@
         <v>0</v>
       </c>
       <c r="I112" s="38">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="J112" s="40">
-        <v>108</v>
+        <v>494</v>
       </c>
       <c r="K112" s="40">
-        <v>127</v>
+        <v>490</v>
       </c>
       <c r="L112" s="40">
         <v>0</v>
@@ -12887,14 +13222,17 @@
       <c r="B113" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C113" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D113" s="36" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="E113" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F113" s="38">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G113" s="38">
         <v>0</v>
@@ -12903,16 +13241,16 @@
         <v>0</v>
       </c>
       <c r="I113" s="38">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J113" s="40">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="K113" s="40">
-        <v>12</v>
+        <v>523</v>
       </c>
       <c r="L113" s="40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="40">
         <v>0</v>
@@ -12925,29 +13263,32 @@
       <c r="B114" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C114" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D114" s="36" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="E114" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F114" s="38">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G114" s="38">
-        <v>0</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="H114" s="39">
-        <v>0</v>
+        <v>1.8500000000000003E-2</v>
       </c>
       <c r="I114" s="38">
-        <v>1</v>
+        <v>58.89</v>
       </c>
       <c r="J114" s="40">
-        <v>138</v>
+        <v>500</v>
       </c>
       <c r="K114" s="40">
-        <v>138</v>
+        <v>537.70000000000005</v>
       </c>
       <c r="L114" s="40">
         <v>0</v>
@@ -12963,35 +13304,38 @@
       <c r="B115" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C115" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D115" s="36" t="s">
-        <v>189</v>
+        <v>28</v>
       </c>
       <c r="E115" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F115" s="38">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G115" s="38">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="H115" s="39">
-        <v>0</v>
+        <v>9.4E-2</v>
       </c>
       <c r="I115" s="38">
-        <v>1</v>
+        <v>54.36</v>
       </c>
       <c r="J115" s="40">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K115" s="40">
-        <v>0</v>
+        <v>565.6</v>
       </c>
       <c r="L115" s="40">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M115" s="40">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13001,14 +13345,17 @@
       <c r="B116" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C116" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D116" s="36" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="E116" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F116" s="38">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G116" s="38">
         <v>0</v>
@@ -13017,19 +13364,19 @@
         <v>0</v>
       </c>
       <c r="I116" s="38">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J116" s="40">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="K116" s="40">
-        <v>2</v>
+        <v>575</v>
       </c>
       <c r="L116" s="40">
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="M116" s="40">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13039,29 +13386,32 @@
       <c r="B117" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C117" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="D117" s="36" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="E117" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F117" s="38">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G117" s="38">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="H117" s="39">
-        <v>0</v>
+        <v>8.3499999999999991E-2</v>
       </c>
       <c r="I117" s="38">
-        <v>1</v>
+        <v>54.99</v>
       </c>
       <c r="J117" s="40">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="K117" s="40">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="L117" s="40">
         <v>0</v>
@@ -13077,14 +13427,17 @@
       <c r="B118" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C118" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D118" s="36" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E118" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F118" s="38">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G118" s="38">
         <v>0</v>
@@ -13093,16 +13446,16 @@
         <v>0</v>
       </c>
       <c r="I118" s="38">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J118" s="40">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="K118" s="40">
-        <v>50</v>
+        <v>818</v>
       </c>
       <c r="L118" s="40">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="M118" s="40">
         <v>0</v>
@@ -13115,32 +13468,35 @@
       <c r="B119" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C119" s="36" t="s">
+        <v>173</v>
+      </c>
       <c r="D119" s="36" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="E119" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F119" s="38">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G119" s="38">
-        <v>0</v>
+        <v>17.45</v>
       </c>
       <c r="H119" s="39">
-        <v>0</v>
+        <v>0.17449999999999999</v>
       </c>
       <c r="I119" s="38">
-        <v>10</v>
+        <v>82.55</v>
       </c>
       <c r="J119" s="40">
-        <v>144</v>
+        <v>500</v>
       </c>
       <c r="K119" s="40">
-        <v>139</v>
+        <v>956.2</v>
       </c>
       <c r="L119" s="40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M119" s="40">
         <v>0</v>
@@ -13153,38 +13509,44 @@
       <c r="B120" s="36" t="s">
         <v>222</v>
       </c>
+      <c r="C120" s="36" t="s">
+        <v>187</v>
+      </c>
       <c r="D120" s="36" t="s">
-        <v>133</v>
+        <v>196</v>
       </c>
       <c r="E120" s="37">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="F120" s="38">
+        <v>140</v>
+      </c>
+      <c r="G120" s="38">
+        <v>10.3</v>
+      </c>
+      <c r="H120" s="39">
+        <v>7.3571428571428579E-2</v>
+      </c>
+      <c r="I120" s="38">
+        <v>129.69999999999999</v>
+      </c>
+      <c r="J120" s="40">
+        <v>500</v>
+      </c>
+      <c r="K120" s="40">
+        <v>1061.8</v>
+      </c>
+      <c r="L120" s="40">
+        <v>891</v>
+      </c>
+      <c r="M120" s="40">
         <v>1</v>
       </c>
-      <c r="G120" s="38">
-        <v>0</v>
-      </c>
-      <c r="H120" s="39">
-        <v>0</v>
-      </c>
-      <c r="I120" s="38">
-        <v>1</v>
-      </c>
-      <c r="J120" s="40">
-        <v>8</v>
-      </c>
-      <c r="K120" s="40">
-        <v>8</v>
-      </c>
-      <c r="L120" s="40">
-        <v>0</v>
-      </c>
-      <c r="M120" s="40">
-        <v>8</v>
-      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M120">
+    <sortCondition ref="K2:K120"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13194,7 +13556,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="12" bestFit="1" customWidth="1"/>
@@ -13240,10 +13602,10 @@
         <v>230</v>
       </c>
       <c r="F2" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G2" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13263,10 +13625,10 @@
         <v>230</v>
       </c>
       <c r="F3" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G3" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13286,10 +13648,10 @@
         <v>230</v>
       </c>
       <c r="F4" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G4" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13309,10 +13671,10 @@
         <v>230</v>
       </c>
       <c r="F5" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G5" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13332,10 +13694,10 @@
         <v>230</v>
       </c>
       <c r="F6" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G6" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13355,10 +13717,10 @@
         <v>230</v>
       </c>
       <c r="F7" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G7" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13378,10 +13740,10 @@
         <v>230</v>
       </c>
       <c r="F8" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G8" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13401,10 +13763,10 @@
         <v>230</v>
       </c>
       <c r="F9" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G9" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13424,10 +13786,10 @@
         <v>230</v>
       </c>
       <c r="F10" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G10" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13447,10 +13809,10 @@
         <v>230</v>
       </c>
       <c r="F11" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G11" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13470,10 +13832,10 @@
         <v>230</v>
       </c>
       <c r="F12" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G12" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13493,10 +13855,10 @@
         <v>230</v>
       </c>
       <c r="F13" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G13" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13516,10 +13878,10 @@
         <v>230</v>
       </c>
       <c r="F14" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G14" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13539,10 +13901,10 @@
         <v>230</v>
       </c>
       <c r="F15" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G15" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13562,10 +13924,10 @@
         <v>230</v>
       </c>
       <c r="F16" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G16" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13585,10 +13947,10 @@
         <v>230</v>
       </c>
       <c r="F17" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G17" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13608,10 +13970,10 @@
         <v>230</v>
       </c>
       <c r="F18" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G18" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13631,10 +13993,10 @@
         <v>230</v>
       </c>
       <c r="F19" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G19" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13654,10 +14016,10 @@
         <v>230</v>
       </c>
       <c r="F20" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G20" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13677,10 +14039,10 @@
         <v>230</v>
       </c>
       <c r="F21" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G21" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13700,10 +14062,10 @@
         <v>230</v>
       </c>
       <c r="F22" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G22" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13723,10 +14085,10 @@
         <v>230</v>
       </c>
       <c r="F23" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G23" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13746,10 +14108,10 @@
         <v>230</v>
       </c>
       <c r="F24" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G24" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13769,10 +14131,10 @@
         <v>230</v>
       </c>
       <c r="F25" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G25" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13792,10 +14154,10 @@
         <v>230</v>
       </c>
       <c r="F26" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G26" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13815,10 +14177,10 @@
         <v>230</v>
       </c>
       <c r="F27" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G27" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13838,10 +14200,10 @@
         <v>230</v>
       </c>
       <c r="F28" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G28" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13861,10 +14223,10 @@
         <v>230</v>
       </c>
       <c r="F29" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G29" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13884,10 +14246,10 @@
         <v>230</v>
       </c>
       <c r="F30" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G30" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13907,10 +14269,10 @@
         <v>230</v>
       </c>
       <c r="F31" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G31" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13930,10 +14292,10 @@
         <v>230</v>
       </c>
       <c r="F32" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G32" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13953,10 +14315,10 @@
         <v>230</v>
       </c>
       <c r="F33" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G33" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13976,10 +14338,10 @@
         <v>230</v>
       </c>
       <c r="F34" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G34" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13999,10 +14361,10 @@
         <v>230</v>
       </c>
       <c r="F35" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G35" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14022,10 +14384,10 @@
         <v>230</v>
       </c>
       <c r="F36" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G36" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14045,10 +14407,10 @@
         <v>230</v>
       </c>
       <c r="F37" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G37" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14068,10 +14430,10 @@
         <v>230</v>
       </c>
       <c r="F38" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G38" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14091,10 +14453,10 @@
         <v>230</v>
       </c>
       <c r="F39" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G39" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14114,10 +14476,10 @@
         <v>230</v>
       </c>
       <c r="F40" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G40" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14137,10 +14499,10 @@
         <v>230</v>
       </c>
       <c r="F41" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G41" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14160,10 +14522,10 @@
         <v>230</v>
       </c>
       <c r="F42" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G42" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14183,10 +14545,10 @@
         <v>230</v>
       </c>
       <c r="F43" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G43" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14206,10 +14568,10 @@
         <v>230</v>
       </c>
       <c r="F44" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G44" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14229,10 +14591,10 @@
         <v>230</v>
       </c>
       <c r="F45" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G45" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14252,10 +14614,10 @@
         <v>230</v>
       </c>
       <c r="F46" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G46" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14275,10 +14637,10 @@
         <v>230</v>
       </c>
       <c r="F47" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G47" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14298,10 +14660,10 @@
         <v>230</v>
       </c>
       <c r="F48" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G48" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14321,10 +14683,10 @@
         <v>230</v>
       </c>
       <c r="F49" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G49" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14344,10 +14706,10 @@
         <v>230</v>
       </c>
       <c r="F50" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G50" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14367,10 +14729,10 @@
         <v>230</v>
       </c>
       <c r="F51" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G51" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14390,10 +14752,10 @@
         <v>230</v>
       </c>
       <c r="F52" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G52" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14413,10 +14775,10 @@
         <v>230</v>
       </c>
       <c r="F53" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G53" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14436,10 +14798,10 @@
         <v>230</v>
       </c>
       <c r="F54" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G54" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14459,10 +14821,10 @@
         <v>230</v>
       </c>
       <c r="F55" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G55" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14482,10 +14844,10 @@
         <v>230</v>
       </c>
       <c r="F56" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G56" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14505,10 +14867,10 @@
         <v>230</v>
       </c>
       <c r="F57" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G57" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14528,10 +14890,10 @@
         <v>230</v>
       </c>
       <c r="F58" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G58" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14551,10 +14913,10 @@
         <v>230</v>
       </c>
       <c r="F59" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G59" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14574,10 +14936,10 @@
         <v>230</v>
       </c>
       <c r="F60" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G60" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14597,10 +14959,10 @@
         <v>230</v>
       </c>
       <c r="F61" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G61" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14620,10 +14982,10 @@
         <v>230</v>
       </c>
       <c r="F62" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G62" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14643,10 +15005,10 @@
         <v>230</v>
       </c>
       <c r="F63" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G63" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14666,10 +15028,10 @@
         <v>230</v>
       </c>
       <c r="F64" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G64" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14689,10 +15051,10 @@
         <v>230</v>
       </c>
       <c r="F65" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G65" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14712,10 +15074,10 @@
         <v>230</v>
       </c>
       <c r="F66" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G66" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14735,10 +15097,10 @@
         <v>230</v>
       </c>
       <c r="F67" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G67" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14758,10 +15120,10 @@
         <v>230</v>
       </c>
       <c r="F68" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G68" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14781,10 +15143,10 @@
         <v>230</v>
       </c>
       <c r="F69" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G69" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14804,10 +15166,10 @@
         <v>230</v>
       </c>
       <c r="F70" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G70" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14827,10 +15189,10 @@
         <v>230</v>
       </c>
       <c r="F71" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G71" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14850,10 +15212,10 @@
         <v>230</v>
       </c>
       <c r="F72" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G72" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14873,10 +15235,10 @@
         <v>230</v>
       </c>
       <c r="F73" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G73" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14896,10 +15258,10 @@
         <v>230</v>
       </c>
       <c r="F74" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G74" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14919,10 +15281,10 @@
         <v>230</v>
       </c>
       <c r="F75" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G75" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14942,10 +15304,10 @@
         <v>230</v>
       </c>
       <c r="F76" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G76" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14965,10 +15327,10 @@
         <v>230</v>
       </c>
       <c r="F77" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G77" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14988,10 +15350,10 @@
         <v>230</v>
       </c>
       <c r="F78" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G78" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15011,10 +15373,10 @@
         <v>230</v>
       </c>
       <c r="F79" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G79" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15034,10 +15396,10 @@
         <v>230</v>
       </c>
       <c r="F80" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G80" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15057,10 +15419,10 @@
         <v>230</v>
       </c>
       <c r="F81" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G81" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15080,10 +15442,10 @@
         <v>230</v>
       </c>
       <c r="F82" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G82" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15103,10 +15465,10 @@
         <v>230</v>
       </c>
       <c r="F83" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G83" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15126,10 +15488,10 @@
         <v>230</v>
       </c>
       <c r="F84" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G84" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15149,10 +15511,10 @@
         <v>230</v>
       </c>
       <c r="F85" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G85" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15172,10 +15534,10 @@
         <v>230</v>
       </c>
       <c r="F86" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G86" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15195,10 +15557,10 @@
         <v>230</v>
       </c>
       <c r="F87" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G87" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15218,10 +15580,10 @@
         <v>230</v>
       </c>
       <c r="F88" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G88" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15241,10 +15603,10 @@
         <v>230</v>
       </c>
       <c r="F89" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G89" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15264,10 +15626,10 @@
         <v>230</v>
       </c>
       <c r="F90" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G90" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15287,10 +15649,10 @@
         <v>230</v>
       </c>
       <c r="F91" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G91" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15310,10 +15672,10 @@
         <v>230</v>
       </c>
       <c r="F92" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G92" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15333,10 +15695,10 @@
         <v>230</v>
       </c>
       <c r="F93" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G93" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15356,10 +15718,10 @@
         <v>230</v>
       </c>
       <c r="F94" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G94" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15379,10 +15741,10 @@
         <v>230</v>
       </c>
       <c r="F95" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G95" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15402,10 +15764,10 @@
         <v>230</v>
       </c>
       <c r="F96" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G96" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15425,10 +15787,10 @@
         <v>230</v>
       </c>
       <c r="F97" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G97" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15448,10 +15810,10 @@
         <v>230</v>
       </c>
       <c r="F98" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G98" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15471,10 +15833,10 @@
         <v>230</v>
       </c>
       <c r="F99" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G99" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15494,10 +15856,10 @@
         <v>230</v>
       </c>
       <c r="F100" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G100" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15517,10 +15879,10 @@
         <v>230</v>
       </c>
       <c r="F101" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G101" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15540,10 +15902,10 @@
         <v>230</v>
       </c>
       <c r="F102" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G102" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15563,10 +15925,10 @@
         <v>230</v>
       </c>
       <c r="F103" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G103" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15586,10 +15948,10 @@
         <v>230</v>
       </c>
       <c r="F104" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G104" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15609,10 +15971,10 @@
         <v>230</v>
       </c>
       <c r="F105" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G105" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15632,10 +15994,10 @@
         <v>230</v>
       </c>
       <c r="F106" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G106" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15655,10 +16017,10 @@
         <v>230</v>
       </c>
       <c r="F107" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G107" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15678,10 +16040,10 @@
         <v>230</v>
       </c>
       <c r="F108" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G108" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15701,10 +16063,10 @@
         <v>230</v>
       </c>
       <c r="F109" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G109" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15724,10 +16086,10 @@
         <v>230</v>
       </c>
       <c r="F110" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G110" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15747,10 +16109,10 @@
         <v>230</v>
       </c>
       <c r="F111" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G111" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15770,10 +16132,10 @@
         <v>230</v>
       </c>
       <c r="F112" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G112" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15793,10 +16155,10 @@
         <v>230</v>
       </c>
       <c r="F113" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G113" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15816,10 +16178,10 @@
         <v>230</v>
       </c>
       <c r="F114" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G114" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15839,10 +16201,10 @@
         <v>230</v>
       </c>
       <c r="F115" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G115" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15862,10 +16224,10 @@
         <v>230</v>
       </c>
       <c r="F116" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G116" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15885,10 +16247,10 @@
         <v>230</v>
       </c>
       <c r="F117" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G117" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15908,10 +16270,10 @@
         <v>230</v>
       </c>
       <c r="F118" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G118" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15919,10 +16281,10 @@
         <v>222</v>
       </c>
       <c r="B119" s="36" t="s">
-        <v>348</v>
+        <v>415</v>
       </c>
       <c r="C119" s="36" t="s">
-        <v>119</v>
+        <v>416</v>
       </c>
       <c r="D119" s="36" t="s">
         <v>229</v>
@@ -15931,10 +16293,10 @@
         <v>230</v>
       </c>
       <c r="F119" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G119" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15942,10 +16304,10 @@
         <v>222</v>
       </c>
       <c r="B120" s="36" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C120" s="36" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="D120" s="36" t="s">
         <v>229</v>
@@ -15954,10 +16316,10 @@
         <v>230</v>
       </c>
       <c r="F120" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G120" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15965,10 +16327,10 @@
         <v>222</v>
       </c>
       <c r="B121" s="36" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C121" s="36" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="D121" s="36" t="s">
         <v>229</v>
@@ -15977,10 +16339,10 @@
         <v>230</v>
       </c>
       <c r="F121" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G121" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15988,10 +16350,10 @@
         <v>222</v>
       </c>
       <c r="B122" s="36" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C122" s="36" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D122" s="36" t="s">
         <v>229</v>
@@ -16000,10 +16362,10 @@
         <v>230</v>
       </c>
       <c r="F122" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G122" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16011,10 +16373,10 @@
         <v>222</v>
       </c>
       <c r="B123" s="36" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C123" s="36" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D123" s="36" t="s">
         <v>229</v>
@@ -16023,10 +16385,10 @@
         <v>230</v>
       </c>
       <c r="F123" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G123" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16034,10 +16396,10 @@
         <v>222</v>
       </c>
       <c r="B124" s="36" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C124" s="36" t="s">
-        <v>354</v>
+        <v>100</v>
       </c>
       <c r="D124" s="36" t="s">
         <v>229</v>
@@ -16046,10 +16408,10 @@
         <v>230</v>
       </c>
       <c r="F124" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G124" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16057,10 +16419,10 @@
         <v>222</v>
       </c>
       <c r="B125" s="36" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C125" s="36" t="s">
-        <v>201</v>
+        <v>354</v>
       </c>
       <c r="D125" s="36" t="s">
         <v>229</v>
@@ -16069,10 +16431,10 @@
         <v>230</v>
       </c>
       <c r="F125" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G125" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16080,10 +16442,10 @@
         <v>222</v>
       </c>
       <c r="B126" s="36" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C126" s="36" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="D126" s="36" t="s">
         <v>229</v>
@@ -16092,10 +16454,10 @@
         <v>230</v>
       </c>
       <c r="F126" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G126" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16103,10 +16465,10 @@
         <v>222</v>
       </c>
       <c r="B127" s="36" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C127" s="36" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D127" s="36" t="s">
         <v>229</v>
@@ -16115,10 +16477,10 @@
         <v>230</v>
       </c>
       <c r="F127" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G127" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16126,10 +16488,10 @@
         <v>222</v>
       </c>
       <c r="B128" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C128" s="36" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D128" s="36" t="s">
         <v>229</v>
@@ -16138,10 +16500,10 @@
         <v>230</v>
       </c>
       <c r="F128" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G128" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16149,10 +16511,10 @@
         <v>222</v>
       </c>
       <c r="B129" s="36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C129" s="36" t="s">
-        <v>185</v>
+        <v>109</v>
       </c>
       <c r="D129" s="36" t="s">
         <v>229</v>
@@ -16161,10 +16523,10 @@
         <v>230</v>
       </c>
       <c r="F129" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G129" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16172,10 +16534,10 @@
         <v>222</v>
       </c>
       <c r="B130" s="36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C130" s="36" t="s">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="D130" s="36" t="s">
         <v>229</v>
@@ -16184,10 +16546,10 @@
         <v>230</v>
       </c>
       <c r="F130" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G130" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16195,10 +16557,10 @@
         <v>222</v>
       </c>
       <c r="B131" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C131" s="36" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="D131" s="36" t="s">
         <v>229</v>
@@ -16207,10 +16569,10 @@
         <v>230</v>
       </c>
       <c r="F131" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G131" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16218,10 +16580,10 @@
         <v>222</v>
       </c>
       <c r="B132" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C132" s="36" t="s">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="D132" s="36" t="s">
         <v>229</v>
@@ -16230,10 +16592,10 @@
         <v>230</v>
       </c>
       <c r="F132" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G132" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16241,10 +16603,10 @@
         <v>222</v>
       </c>
       <c r="B133" s="36" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C133" s="36" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D133" s="36" t="s">
         <v>229</v>
@@ -16253,10 +16615,10 @@
         <v>230</v>
       </c>
       <c r="F133" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G133" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16264,10 +16626,10 @@
         <v>222</v>
       </c>
       <c r="B134" s="36" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C134" s="36" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="D134" s="36" t="s">
         <v>229</v>
@@ -16276,10 +16638,10 @@
         <v>230</v>
       </c>
       <c r="F134" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G134" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16287,10 +16649,10 @@
         <v>222</v>
       </c>
       <c r="B135" s="36" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C135" s="36" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D135" s="36" t="s">
         <v>229</v>
@@ -16299,10 +16661,10 @@
         <v>230</v>
       </c>
       <c r="F135" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G135" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16310,10 +16672,10 @@
         <v>222</v>
       </c>
       <c r="B136" s="36" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C136" s="36" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="D136" s="36" t="s">
         <v>229</v>
@@ -16322,10 +16684,10 @@
         <v>230</v>
       </c>
       <c r="F136" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G136" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16333,10 +16695,10 @@
         <v>222</v>
       </c>
       <c r="B137" s="36" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C137" s="36" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="D137" s="36" t="s">
         <v>229</v>
@@ -16345,10 +16707,33 @@
         <v>230</v>
       </c>
       <c r="F137" s="41">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="G137" s="41">
-        <v>46070</v>
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="B138" s="36" t="s">
+        <v>367</v>
+      </c>
+      <c r="C138" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D138" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E138" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="F138" s="41">
+        <v>46076</v>
+      </c>
+      <c r="G138" s="41">
+        <v>46076</v>
       </c>
     </row>
   </sheetData>
